--- a/Result/profitability/8093.xlsx
+++ b/Result/profitability/8093.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.1</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.36125</v>
+        <v>-0.30375</v>
       </c>
       <c r="N2" t="n">
-        <v>20.00625</v>
+        <v>22.32875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.17</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.27125</v>
+        <v>-0.24125</v>
       </c>
       <c r="N3" t="n">
-        <v>24.84</v>
+        <v>25.19</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.2</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1625</v>
+        <v>-0.25</v>
       </c>
       <c r="N4" t="n">
-        <v>27.3925</v>
+        <v>24.5575</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1575</v>
+        <v>-0.17625</v>
       </c>
       <c r="N5" t="n">
-        <v>29.3375</v>
+        <v>28.38125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1075</v>
+        <v>-0.10625</v>
       </c>
       <c r="N6" t="n">
-        <v>31.74</v>
+        <v>29.8475</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.17</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03125</v>
+        <v>-0.015</v>
       </c>
       <c r="N7" t="n">
-        <v>33.12125</v>
+        <v>33.39125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.5</v>
       </c>
       <c r="M8" t="n">
-        <v>0.10125</v>
+        <v>0.1</v>
       </c>
       <c r="N8" t="n">
-        <v>37.285</v>
+        <v>36.83</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1902,7 +1902,7 @@
         <v>0.1175</v>
       </c>
       <c r="N12" t="n">
-        <v>44.01000000000001</v>
+        <v>44.01</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>-0.14</v>
       </c>
       <c r="M13" t="n">
-        <v>0.06125</v>
+        <v>0.06124999999999999</v>
       </c>
       <c r="N13" t="n">
         <v>41.60125</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8093</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>64</v>
+      </c>
+      <c r="D75" t="n">
+        <v>56</v>
+      </c>
+      <c r="E75" t="n">
+        <v>8</v>
+      </c>
+      <c r="F75" t="n">
+        <v>13.17</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-19</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-29.03%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-15</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-17</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.4275</v>
+      </c>
+      <c r="N75" t="n">
+        <v>16.36625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.01000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.02380952380952372</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.639999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.2165377751338489</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.5357142857142856</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-7.65</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.3674351585014409</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
